--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0220.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0220.xlsx
@@ -10460,7 +10460,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Gì?</t>
         </is>
       </c>
     </row>
@@ -11955,7 +11955,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>&lt;color=#56e2e7&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -12085,7 +12085,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Remaining: {0}</t>
+          <t>Còn lại: {0}</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Giai đoạn này sẽ mở khóa trong {0}.</t>
+          <t>Giai đoạn này sẽ mở khóa vào {0}.</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Cộng Hưởng Giả lên Lv. 50.</t>
+          <t>Nâng cấp 1 Resonator lên Lv. 50.</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Cộng Hưởng Giả lên cấp 60.</t>
+          <t>Nâng cấp 1 Resonator lên cấp 60.</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Cộng Hưởng Giả lên cấp 70.</t>
+          <t>Nâng cấp 1 Resonator lên cấp 70.</t>
         </is>
       </c>
     </row>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Cộng Hưởng Giả lên cấp 80.</t>
+          <t>Nâng cấp 1 Resonator lên cấp 80.</t>
         </is>
       </c>
     </row>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Nâng cấp 2 Cộng Hưởng Giả lên cấp 80.</t>
+          <t>Nâng cấp 2 Resonator lên cấp 80.</t>
         </is>
       </c>
     </row>
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Trạng Thái Hiện Tại: Thiết bị đầu cuối đang được lưu trữ. Mô-đun dữ liệu lõi đã tách rời và thất lạc.</t>
+          <t>Trạng Thái Hiện Tại: Terminal is in storage. Core data module is detached and missing.</t>
         </is>
       </c>
     </row>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Giai đoạn này sẽ mở khóa trong {0}.</t>
+          <t>Giai đoạn này sẽ mở khóa vào {0}.</t>
         </is>
       </c>
     </row>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Highest Record: {0}</t>
+          <t>Kỷ Lục Cao Nhất: {0}</t>
         </is>
       </c>
     </row>
@@ -21979,7 +21979,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>&lt;color=#fde7a1&gt;{0}&lt;/color&gt;&lt;color=#ece5d8&gt;/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>&lt;color=#fde7a1&gt;{0}&lt;/color&gt;&lt;color=#ece5d8&gt;/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>&lt;color=#ece5d8&gt;Max&lt;/color&gt;</t>
+          <t>&lt;color=#ece5d8&gt;Tối Đa&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>&lt;color=#fde7a1&gt;{0}&lt;/color&gt;&lt;color=#ece5d8&gt;/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -22564,7 +22564,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Full Metal Cảnh báo!</t>
+          <t>Báo Động Toàn Thân Kim Loại!</t>
         </is>
       </c>
     </row>
@@ -25489,7 +25489,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Nhạc nền trong trận chiến với Fallacy of Không Return.</t>
+          <t>Nhạc nền trong trận chiến với Fallacy of No Return.</t>
         </is>
       </c>
     </row>
@@ -27634,7 +27634,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Nhạc nền Lâu đài Porto-Veno.</t>
+          <t>Nhạc nền Porto-Veno Castle.</t>
         </is>
       </c>
     </row>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Nhạc nền Lâu đài Porto-Veno.</t>
+          <t>Nhạc nền Porto-Veno Castle.</t>
         </is>
       </c>
     </row>
